--- a/artfynd/A 33797-2024 artfynd.xlsx
+++ b/artfynd/A 33797-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1406,66 +1406,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117479592</v>
+        <v>137433884</v>
       </c>
       <c r="B9" t="n">
-        <v>58817</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208249</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ramkvilla Nygård, Sm</t>
+          <t>Nygård, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497275</v>
+        <v>497270</v>
       </c>
       <c r="R9" t="n">
-        <v>6340932</v>
+        <v>6340888</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,12 +1471,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,91 +1485,68 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Hällmarksblandskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Mossig mark med äldre träd av framförallt tall och gran, med uttorkad bäck. Området omgivet av högre hällmark och klippor.</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>James Bonet</t>
+          <t>Janne Kolehmainen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>James Bonet</t>
+          <t>Janne Kolehmainen, Pontus Axén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117479592</t>
+          <t>https://artportalen.se/Sighting/137433884</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96153856</v>
+        <v>137432809</v>
       </c>
       <c r="B10" t="n">
-        <v>99118</v>
+        <v>83507</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>NO om Ramkvilla, Sm</t>
+          <t>Nygård, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497311</v>
+        <v>497298</v>
       </c>
       <c r="R10" t="n">
-        <v>6341014</v>
+        <v>6340909</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,12 +1573,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-05</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-05</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1631,75 +1587,89 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Pontus Axén</t>
+          <t>Janne Kolehmainen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Pontus Axén</t>
+          <t>Janne Kolehmainen, Pontus Axén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96153856</t>
+          <t>https://artportalen.se/Sighting/137432809</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96516469</v>
+        <v>117479592</v>
       </c>
       <c r="B11" t="n">
-        <v>99118</v>
+        <v>58817</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>NO om Ramkvilla, Sm</t>
+          <t>Ramkvilla Nygård, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497290</v>
+        <v>497275</v>
       </c>
       <c r="R11" t="n">
-        <v>6341063</v>
+        <v>6340932</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1726,12 +1696,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-09-05</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-09-05</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,30 +1710,41 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Hällmarksblandskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Mossig mark med äldre träd av framförallt tall och gran, med uttorkad bäck. Området omgivet av högre hällmark och klippor.</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Pontus Axén</t>
+          <t>James Bonet</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Pontus Axén</t>
+          <t>James Bonet</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96516469</t>
+          <t>https://artportalen.se/Sighting/117479592</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119151902</v>
+        <v>96153856</v>
       </c>
       <c r="B12" t="n">
         <v>99118</v>
@@ -1793,23 +1774,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nygård, Sm</t>
+          <t>NO om Ramkvilla, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497238</v>
+        <v>497311</v>
       </c>
       <c r="R12" t="n">
-        <v>6341021</v>
+        <v>6341014</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,12 +1821,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2021-09-05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2021-09-05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1868,13 +1853,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119151902</t>
+          <t>https://artportalen.se/Sighting/96153856</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119152023</v>
+        <v>96516469</v>
       </c>
       <c r="B13" t="n">
         <v>99118</v>
@@ -1904,27 +1889,21 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nygård, Sm</t>
+          <t>NO om Ramkvilla, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497276</v>
+        <v>497290</v>
       </c>
       <c r="R13" t="n">
-        <v>6340957</v>
+        <v>6341063</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,12 +1930,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2021-09-05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2021-09-05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1965,7 +1944,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1983,13 +1961,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119152023</t>
+          <t>https://artportalen.se/Sighting/96516469</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119335936</v>
+        <v>119151902</v>
       </c>
       <c r="B14" t="n">
         <v>99118</v>
@@ -2019,35 +1997,23 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nygård, Ramkvilla, Sm</t>
+          <t>Nygård, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497265</v>
+        <v>497238</v>
       </c>
       <c r="R14" t="n">
-        <v>6340995</v>
+        <v>6341021</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2074,12 +2040,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2092,24 +2058,262 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>James Bonet</t>
+          <t>Pontus Axén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>James Bonet</t>
+          <t>Pontus Axén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119151902</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>119152023</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nygård, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>497276</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6340957</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramkvilla</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119152023</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>119335936</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nygård, Ramkvilla, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>497265</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6340995</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramkvilla</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>James Bonet</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>James Bonet</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119335936</t>
         </is>
@@ -2130,6 +2334,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33797-2024 artfynd.xlsx
+++ b/artfynd/A 33797-2024 artfynd.xlsx
@@ -1409,7 +1409,7 @@
         <v>137433884</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>137432809</v>
       </c>
       <c r="B10" t="n">
-        <v>83507</v>
+        <v>83509</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33797-2024 artfynd.xlsx
+++ b/artfynd/A 33797-2024 artfynd.xlsx
@@ -1409,7 +1409,7 @@
         <v>137433884</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>137432809</v>
       </c>
       <c r="B10" t="n">
-        <v>83509</v>
+        <v>83513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
